--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/Residentes Muestreo Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/Residentes Muestreo Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3443CC55-9EC9-45F8-976C-92907EB56DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2648ED-3831-45D6-96E8-7DB85ACC79A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2100" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A03FCC9F-8ADB-4317-A3D3-F6E5CE84BC70}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A03FCC9F-8ADB-4317-A3D3-F6E5CE84BC70}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -490,9 +490,9 @@
       <sheetName val="ZonaComun"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="4">
           <cell r="E4" t="str">
@@ -535,8 +535,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -860,13 +860,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955E1381-9DD8-476B-8044-3E079F79E259}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="58.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -882,7 +882,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -902,21 +902,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74F213F-7D77-4A77-8569-EB0D1E5DC4A2}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="6" width="21.7109375" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="50.5703125" customWidth="1"/>
+    <col min="3" max="6" width="21.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="10" max="10" width="50.5546875" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
     <col min="13" max="13" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>3</v>
       </c>
@@ -930,7 +930,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:13" s="18" customFormat="1" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="18" customFormat="1" ht="69" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>4</v>
       </c>
@@ -971,7 +971,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>example@example.com</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>2</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v xml:space="preserve">ejemplo@jueves.com </v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>andresjobpk@gmail.com</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>alejandro.perez90@mail.com</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>maria.gomez85@mail.com</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>juan.rodriguez95@mail.com</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>7</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>camila.torres00@mail.com</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>8</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>andres.garcia92@mail.com</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>9</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>laura.martinez93@mail.com</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
@@ -1498,16 +1498,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FC3312-8668-46CD-8DD2-1497244E5D47}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
-    <col min="5" max="5" width="49.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="5" max="5" width="49.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>3</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="D1" s="22"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="54" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>68</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="20">
         <v>1</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>Apartamento102 - Torre1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>Casa10 - Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="21">
         <v>3</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>Apartamento304 - Torre2 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>Casa11 - Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="21">
         <v>5</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>Apartamento423 - Bloque1 - Ventus</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>Apartamento1204 - Torre1 - Bolivar</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>Casa5 - Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="20">
         <v>8</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>Casa17 - Bloque2 - Riogrande</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="21">
         <v>9</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>Apartamento514 - Bloque1 - Riogrande</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="21">
         <v>10</v>
       </c>

--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/Residentes Muestreo Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/Residentes Muestreo Datos.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2648ED-3831-45D6-96E8-7DB85ACC79A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CF4D1F-55CB-402F-B159-AE6A8D3D364B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A03FCC9F-8ADB-4317-A3D3-F6E5CE84BC70}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A03FCC9F-8ADB-4317-A3D3-F6E5CE84BC70}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
     <sheet name="Residente" sheetId="2" r:id="rId2"/>
     <sheet name="Inmueble" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
   <si>
     <t>Nombre</t>
   </si>
@@ -115,12 +112,6 @@
     <t>Tarjeta de Identidad</t>
   </si>
   <si>
-    <t>tipoInmueble</t>
-  </si>
-  <si>
-    <t>ZonaInmueble</t>
-  </si>
-  <si>
     <t>Combinación única 1</t>
   </si>
   <si>
@@ -247,24 +238,6 @@
     <t>apellido</t>
   </si>
   <si>
-    <t>Es un dato que hace que cada inmueble sea único.</t>
-  </si>
-  <si>
-    <t>Es un dato que representa al nombre de un inmueble Casa, apartamento ETC.</t>
-  </si>
-  <si>
-    <t>Este atributo representa el número especifico del inmueble.</t>
-  </si>
-  <si>
-    <t>Es un dato que representa la zona inmueble al cual pertenece el inmueble.</t>
-  </si>
-  <si>
-    <t>No es posible tener mas de un tipo inmueble que tenga el mismo número de vivienda más la misma zona inmueble.</t>
-  </si>
-  <si>
-    <t>numeroVivienda</t>
-  </si>
-  <si>
     <t>este dato representa en forma textual , que tipo de documento tiene el residente como TI, CC, RC, PASS.</t>
   </si>
   <si>
@@ -302,6 +275,105 @@
   </si>
   <si>
     <t xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada conjunto residencial sea único.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa al nombre de un conjunto residencial</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el formato numero entero del numero de la vivienda donde esta hospedado el residente.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el identificador de un tipo de zona inmueble.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el nombre de un tipo de inmueble donde hospeda el residente.</t>
+  </si>
+  <si>
+    <t>es un dato que representa el indetificador de un tipo de zona inmuelble.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el nombre de un tipo de zoba  inmueble donde hospeda el residente.</t>
+  </si>
+  <si>
+    <t>Este dato representa el numero asignado para una zona inmueble de un conjunto residencial</t>
+  </si>
+  <si>
+    <t>No es posiible tener una informacion repetida para la consulta de otro residente.</t>
+  </si>
+  <si>
+    <t>ConjuntoResidencial(Identificador)</t>
+  </si>
+  <si>
+    <t>ConjuntoResidencial(Nombre)</t>
+  </si>
+  <si>
+    <t>Inmueble(NumeroVivienda)</t>
+  </si>
+  <si>
+    <t>TipoInmueble(Identificador)</t>
+  </si>
+  <si>
+    <t>TipoInmueble(Nombre)</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble(Identificador)</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble(Nombre)</t>
+  </si>
+  <si>
+    <t>ZonaInmueble(NumeroZonaInmueble)</t>
+  </si>
+  <si>
+    <t>Forest apartamentos</t>
+  </si>
+  <si>
+    <t>Torre</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>Bloque</t>
+  </si>
+  <si>
+    <t>Riogrande</t>
+  </si>
+  <si>
+    <t>Ventus</t>
+  </si>
+  <si>
+    <t>1Forest apartamentos-1Torre-5-1Apartamento-1204</t>
+  </si>
+  <si>
+    <t>1Forest apartamentos-1Torre-5-1Apartamento-205</t>
+  </si>
+  <si>
+    <t>2Natural-2Bloque-3-2Casa-514</t>
+  </si>
+  <si>
+    <t>2Natural-2Bloque-3-2Casa-23</t>
+  </si>
+  <si>
+    <t>3Riogrande-1Torre-2-1Apartamento-204</t>
+  </si>
+  <si>
+    <t>3Riogrande-2Bloque-8-2Casa-8</t>
+  </si>
+  <si>
+    <t>3Riogrande-1Torre-7-1Apartamento-306</t>
+  </si>
+  <si>
+    <t>3Riogrande-2Bloque-7-2Casa-4</t>
+  </si>
+  <si>
+    <t>5Ventus-1Torre-7-1Apartamento-501</t>
+  </si>
+  <si>
+    <t>5Ventus-2Bloque-1-2Casa-9</t>
   </si>
 </sst>
 </file>
@@ -311,7 +383,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +430,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -391,7 +471,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -414,12 +494,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -438,7 +531,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
@@ -457,6 +549,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -473,73 +576,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Objetos de dominio"/>
-      <sheetName val="Administrador"/>
-      <sheetName val="ConjuntoResidencial"/>
-      <sheetName val="Zonainmueble"/>
-      <sheetName val="Inmueble"/>
-      <sheetName val="ZonaComun"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="4">
-          <cell r="E4" t="str">
-            <v>Torre1 - Forest apartamentos</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="E5" t="str">
-            <v>Bloque1 - Forest apartamentos</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6" t="str">
-            <v>Torre2 - Forest apartamentos</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7" t="str">
-            <v>Bloque1 - Natural</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9" t="str">
-            <v>Bloque1 - Riogrande</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10" t="str">
-            <v>Bloque1 - Ventus</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11" t="str">
-            <v>Torre1 - Bolivar</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12" t="str">
-            <v>Bloque2 - Riogrande</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -879,15 +915,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -908,7 +944,7 @@
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="6" width="21.6640625" customWidth="1"/>
     <col min="7" max="7" width="23.88671875" customWidth="1"/>
-    <col min="8" max="8" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" customWidth="1"/>
     <col min="10" max="10" width="50.5546875" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
@@ -917,12 +953,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -930,45 +966,45 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:13" s="18" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:13" s="17" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>80</v>
+      <c r="M2" s="18" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -976,25 +1012,25 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
@@ -1003,13 +1039,13 @@
         <v>12</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1038,11 +1074,10 @@
         <v>16</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="17" t="str">
-        <f>Inmueble!E4</f>
-        <v>Apartamento102 - Torre1 - Forest apartamentos</v>
+        <v>55</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>102</v>
       </c>
       <c r="K4" s="13" t="str">
         <f>_xlfn.CONCAT(D4,"-",E4)</f>
@@ -1068,7 +1103,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" s="10">
         <v>16513516</v>
@@ -1083,11 +1118,10 @@
         <v>19</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="17" t="str">
-        <f>Inmueble!E5</f>
-        <v>Casa10 - Bloque1 - Forest apartamentos</v>
+        <v>56</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>103</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" ref="K5:K13" si="0">_xlfn.CONCAT(D5,"-",E5)</f>
@@ -1113,7 +1147,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10">
         <v>8552369</v>
@@ -1128,11 +1162,10 @@
         <v>22</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="12" t="str">
-        <f>Inmueble!E6</f>
-        <v>Apartamento304 - Torre2 - Forest apartamentos</v>
+        <v>57</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1152,10 +1185,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>
@@ -1163,21 +1196,20 @@
       <c r="E7" s="5">
         <v>1012345678</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>32944</v>
       </c>
       <c r="G7" s="5">
         <v>3102345678</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="12" t="str">
-        <f>Inmueble!E7</f>
-        <v>Casa11 - Bloque1 - Natural</v>
+        <v>31</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="K7" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1197,32 +1229,31 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" s="5">
         <v>1023456789</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>31253</v>
       </c>
       <c r="G8" s="5">
         <v>3204567890</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="12" t="str">
-        <f>Inmueble!E8</f>
-        <v>Apartamento423 - Bloque1 - Ventus</v>
+        <v>35</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="K8" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1245,7 +1276,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>15</v>
@@ -1253,21 +1284,20 @@
       <c r="E9" s="5">
         <v>1034567890</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>35013</v>
       </c>
       <c r="G9" s="5">
         <v>3156781234</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="12" t="str">
-        <f>Inmueble!E9</f>
-        <v>Apartamento1204 - Torre1 - Bolivar</v>
+        <v>38</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="K9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1287,10 +1317,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>23</v>
@@ -1298,21 +1328,20 @@
       <c r="E10" s="5">
         <v>900123456</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>36560</v>
       </c>
       <c r="G10" s="5">
         <v>3112345678</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="12" t="str">
-        <f>Inmueble!E10</f>
-        <v>Casa5 - Bloque1 - Natural</v>
+        <v>42</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="K10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1332,32 +1361,31 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E11" s="5">
         <v>1045678901</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>33867</v>
       </c>
       <c r="G11" s="5">
         <v>3149876543</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="2" t="str">
-        <f>Inmueble!E11</f>
-        <v>Casa17 - Bloque2 - Riogrande</v>
+        <v>46</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="K11" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1377,10 +1405,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>15</v>
@@ -1388,21 +1416,20 @@
       <c r="E12" s="5">
         <v>1056789012</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>34128</v>
       </c>
       <c r="G12" s="5">
         <v>3135678901</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="2" t="str">
-        <f>Inmueble!E12</f>
-        <v>Apartamento514 - Bloque1 - Riogrande</v>
+        <v>50</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="K12" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1422,10 +1449,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>15</v>
@@ -1433,21 +1460,20 @@
       <c r="E13" s="5">
         <v>1067890123</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>32507</v>
       </c>
       <c r="G13" s="5">
         <v>3123456789</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="2" t="str">
-        <f>Inmueble!E13</f>
-        <v>Casa23 - Bloque1 - Natural</v>
+        <v>54</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="K13" s="13" t="str">
         <f t="shared" si="0"/>
@@ -1497,272 +1523,406 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FC3312-8668-46CD-8DD2-1497244E5D47}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
-    <col min="5" max="5" width="49.44140625" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="43.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" s="22" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1204</v>
+      </c>
+      <c r="D4" s="19">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F4" s="19">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="25">
+        <v>5</v>
+      </c>
+      <c r="I4" s="14" t="str">
+        <f>_xlfn.CONCAT(A4,B4,"-",F4,G4,"-",H4,"-",D4,E4,"-",C4)</f>
+        <v>1Forest apartamentos-1Torre-5-1Apartamento-1204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="5">
+        <v>205</v>
+      </c>
+      <c r="D5" s="19">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="19">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="25">
+        <v>5</v>
+      </c>
+      <c r="I5" s="14" t="str">
+        <f>_xlfn.CONCAT(A5,B5,"-",F5,G5,"-",H5,"-",D5,E5,"-",C5)</f>
+        <v>1Forest apartamentos-1Torre-5-1Apartamento-205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="5">
+        <v>514</v>
+      </c>
+      <c r="D6" s="20">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="20">
+      <c r="F6" s="20">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="26">
+        <v>3</v>
+      </c>
+      <c r="I6" s="14" t="str">
+        <f t="shared" ref="I6:I13" si="0">_xlfn.CONCAT(A6,B6,"-",F6,G6,"-",H6,"-",D6,E6,"-",C6)</f>
+        <v>2Natural-2Bloque-3-2Casa-514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="5">
+        <v>23</v>
+      </c>
+      <c r="D7" s="20">
+        <v>2</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="20">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="26">
+        <v>3</v>
+      </c>
+      <c r="I7" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>2Natural-2Bloque-3-2Casa-23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="5">
+        <v>204</v>
+      </c>
+      <c r="D8" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="5">
-        <v>102</v>
-      </c>
-      <c r="D4" s="2" t="str">
-        <f>[1]Zonainmueble!$E$4</f>
-        <v>Torre1 - Forest apartamentos</v>
-      </c>
-      <c r="E4" s="15" t="str">
-        <f>_xlfn.CONCAT(B4,C4," - ",D4)</f>
-        <v>Apartamento102 - Torre1 - Forest apartamentos</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="21">
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="19">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="26">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <f>[1]Zonainmueble!$E$5</f>
-        <v>Bloque1 - Forest apartamentos</v>
-      </c>
-      <c r="E5" s="15" t="str">
-        <f t="shared" ref="E5:E13" si="0">_xlfn.CONCAT(B5,C5," - ",D5)</f>
-        <v>Casa10 - Bloque1 - Forest apartamentos</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
+      <c r="I8" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-1Torre-2-1Apartamento-204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="5">
-        <v>304</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f>[1]Zonainmueble!$E$6</f>
-        <v>Torre2 - Forest apartamentos</v>
-      </c>
-      <c r="E6" s="15" t="str">
+      <c r="B9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="20">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="20">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="26">
+        <v>8</v>
+      </c>
+      <c r="I9" s="14" t="str">
         <f t="shared" si="0"/>
-        <v>Apartamento304 - Torre2 - Forest apartamentos</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
+        <v>3Riogrande-2Bloque-8-2Casa-8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="5">
+        <v>306</v>
+      </c>
+      <c r="D10" s="19">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="19">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="26">
+        <v>7</v>
+      </c>
+      <c r="I10" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-1Torre-7-1Apartamento-306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f>[1]Zonainmueble!$E$7</f>
-        <v>Bloque1 - Natural</v>
-      </c>
-      <c r="E7" s="15" t="str">
+      <c r="D11" s="20">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="20">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="26">
+        <v>7</v>
+      </c>
+      <c r="I11" s="14" t="str">
         <f t="shared" si="0"/>
-        <v>Casa11 - Bloque1 - Natural</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
+        <v>3Riogrande-2Bloque-7-2Casa-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5">
-        <v>423</v>
-      </c>
-      <c r="D8" s="2" t="str">
-        <f>[1]Zonainmueble!E10</f>
-        <v>Bloque1 - Ventus</v>
-      </c>
-      <c r="E8" s="15" t="str">
+      <c r="B12" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="5">
+        <v>501</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="19">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="26">
+        <v>7</v>
+      </c>
+      <c r="I12" s="14" t="str">
         <f t="shared" si="0"/>
-        <v>Apartamento423 - Bloque1 - Ventus</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1204</v>
-      </c>
-      <c r="D9" s="2" t="str">
-        <f>[1]Zonainmueble!E11</f>
-        <v>Torre1 - Bolivar</v>
-      </c>
-      <c r="E9" s="15" t="str">
+        <v>5Ventus-1Torre-7-1Apartamento-501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="5">
+        <v>9</v>
+      </c>
+      <c r="D13" s="20">
+        <v>2</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="20">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="26">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="str">
         <f t="shared" si="0"/>
-        <v>Apartamento1204 - Torre1 - Bolivar</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="str">
-        <f>[1]Zonainmueble!E7</f>
-        <v>Bloque1 - Natural</v>
-      </c>
-      <c r="E10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Casa5 - Bloque1 - Natural</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="20">
-        <v>8</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="5">
-        <v>17</v>
-      </c>
-      <c r="D11" s="2" t="str">
-        <f>[1]Zonainmueble!E12</f>
-        <v>Bloque2 - Riogrande</v>
-      </c>
-      <c r="E11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Casa17 - Bloque2 - Riogrande</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="5">
-        <v>514</v>
-      </c>
-      <c r="D12" s="2" t="str">
-        <f>[1]Zonainmueble!E9</f>
-        <v>Bloque1 - Riogrande</v>
-      </c>
-      <c r="E12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Apartamento514 - Bloque1 - Riogrande</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="5">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2" t="str">
-        <f>[1]Zonainmueble!E7</f>
-        <v>Bloque1 - Natural</v>
-      </c>
-      <c r="E13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>Casa23 - Bloque1 - Natural</v>
+        <v>5Ventus-2Bloque-1-2Casa-9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B10" xr:uid="{CA6817BB-2012-4EC5-8A49-271F39AAC04B}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E13" xr:uid="{DFB6A6DF-5D35-4C1F-AC06-B2AF199C77AE}">
       <formula1>$A$14:$A$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{8E13AEC1-0713-4A55-B99E-DBF32A7DD325}">
+      <formula1>$A$8:$A$9</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{F119D66D-5968-4254-A523-357AEBC2E086}"/>
-    <hyperlink ref="A1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{BEA8A92B-A5C4-4DFE-8B4E-FDC4C8A48901}"/>
-    <hyperlink ref="D3" location="Zonainmueble!A1" display="ZonaInmueble" xr:uid="{35F2826D-C755-4C7F-B8DC-2DDEB1453050}"/>
-    <hyperlink ref="D4" location="Zonainmueble!A4" display="Zonainmueble!A4" xr:uid="{A1624FE5-2C28-4120-A78B-781905AE515E}"/>
-    <hyperlink ref="D5" location="Zonainmueble!A5" display="Zonainmueble!A5" xr:uid="{ADF3415F-C899-448A-B3BB-0F106B0D56E7}"/>
-    <hyperlink ref="D6" location="Zonainmueble!A6" display="Zonainmueble!A6" xr:uid="{731E913D-B3C7-422C-B2F2-B5B9BB9C1222}"/>
-    <hyperlink ref="D7" location="Zonainmueble!A7" display="Zonainmueble!A7" xr:uid="{EF72E72F-F0CE-466F-8919-00FBA814404A}"/>
-    <hyperlink ref="D8" location="Zonainmueble!A10" display="Zonainmueble!A10" xr:uid="{58DCC9F6-6B15-4B41-A52D-006E111902A5}"/>
-    <hyperlink ref="D9" location="Zonainmueble!A11" display="Zonainmueble!A11" xr:uid="{3DEC5304-17DE-46B0-A1B8-8E053B0EA20B}"/>
-    <hyperlink ref="D10" location="Zonainmueble!A7" display="Zonainmueble!A7" xr:uid="{9FCD591D-0053-442A-B6C8-EC427BCA624B}"/>
-    <hyperlink ref="D11" location="Zonainmueble!A12" display="Zonainmueble!A12" xr:uid="{69EA0A17-D5A0-4F64-AFDA-8119FA0B860E}"/>
-    <hyperlink ref="D12" location="Zonainmueble!A9" display="Zonainmueble!A9" xr:uid="{9D9E7533-FBD6-475E-88DF-0838E065761E}"/>
-    <hyperlink ref="D13" location="Zonainmueble!A7" display="Zonainmueble!A7" xr:uid="{99B6708E-64FB-4ACC-96F7-503745C0CB19}"/>
+    <hyperlink ref="A1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{D2087BA5-45A2-4987-8F2E-08F26AB1D9A4}"/>
+    <hyperlink ref="A1:F1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{F928776B-75C0-458D-ABDF-E09A7EA4D937}"/>
+    <hyperlink ref="I1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{970B4502-B937-4CA5-85F9-F413B1F8C06C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
